--- a/data/Type1/species by biomass/ES_Cantabrian_NIA_Station_22.xlsx
+++ b/data/Type1/species by biomass/ES_Cantabrian_NIA_Station_22.xlsx
@@ -1,33 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Dropbox\0_IEO\Ciencia\ICES\WKBENTH4\5_OUTPUTS\Type_1\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E967CB5-147A-4D60-BCF8-B5FFA01B3778}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Metadata and protocols" sheetId="1" r:id="rId1"/>
-    <sheet name="Species information" sheetId="3" r:id="rId2"/>
-    <sheet name="Time series information" sheetId="4" r:id="rId3"/>
+    <sheet name="Metadata and protocols" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Time series information" sheetId="4" state="visible" r:id="rId3"/>
+    <sheet name="Species information" sheetId="3" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0" refMode="R1C1"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
   <si>
     <t>cl_name</t>
   </si>
@@ -297,23 +285,212 @@
   </si>
   <si>
     <t>2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type_2_year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">station_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">station</t>
+  </si>
+  <si>
+    <t xml:space="preserve">year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">longitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">latitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">depth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">area_sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replicates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">substrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assessment_unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_abundance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_biomass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">richness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rel Margalef div (dens)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rel Margalef div (biom)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SoS_2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">area_sampled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_number_individuals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total_biomass_correct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rel.margalef.div.(dens)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rel.margalef.div.(biom)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_BQI_2009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_22.xlsx_2013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_22_2013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_Station_22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.80146027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">otter_trawl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Circalittoral sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_22.xlsx_2014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_22_2014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.28070831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_22.xlsx_2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_22_2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_22.xlsx_2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_22_2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_22.xlsx_2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_22_2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_22.xlsx_2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_22_2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_22.xlsx_2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_22_2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.99936676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_22.xlsx_2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_22_2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_22.xlsx_2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_22_2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_22.xlsx_2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_22_2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -339,9 +516,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -637,11 +813,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -649,7 +825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -657,7 +833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -665,7 +841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -673,7 +849,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -681,7 +857,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -689,7 +865,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -697,7 +873,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -705,7 +881,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -713,7 +889,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -721,7 +897,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -729,7 +905,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -737,7 +913,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -745,7 +921,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -753,7 +929,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -761,7 +937,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -769,7 +945,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -777,7 +953,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -785,7 +961,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -793,7 +969,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -801,7 +977,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -809,7 +985,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -817,7 +993,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -832,11 +1008,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -865,26 +1041,26 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>40</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>2013</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>29</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>100946</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>1.047127363E-4</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>7.3298915419999996E-4</v>
       </c>
       <c r="H2" t="s">
@@ -894,26 +1070,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>40</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>2013</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="s">
         <v>29</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>107236</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>1.047127363E-4</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>3.4904245439999999E-5</v>
       </c>
       <c r="H3" t="s">
@@ -923,26 +1099,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>40</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>2013</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="s">
         <v>29</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>107239</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>4.3630306800000003E-4</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>1.3089092040000001E-3</v>
       </c>
       <c r="H4" t="s">
@@ -952,26 +1128,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>40</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>2013</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="s">
         <v>29</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>107350</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>1.745212272E-5</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>1.8411989470000001E-2</v>
       </c>
       <c r="H5" t="s">
@@ -981,26 +1157,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>40</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>2013</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="s">
         <v>29</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>123803</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>3.4904245439999999E-5</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>2.8796002489999998E-3</v>
       </c>
       <c r="H6" t="s">
@@ -1010,26 +1186,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>40</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>2013</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>123867</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>1.745212272E-5</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>1.047127363E-4</v>
       </c>
       <c r="H7" t="s">
@@ -1039,26 +1215,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>40</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>2014</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>107342</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>1.7840907629999999E-5</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>1.7840907629999999E-5</v>
       </c>
       <c r="H8" t="s">
@@ -1068,26 +1244,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>40</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>2014</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>123867</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>1.7840907629999999E-5</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>2.8545452209999999E-4</v>
       </c>
       <c r="H9" t="s">
@@ -1097,26 +1273,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>40</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>2015</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>123803</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>1.8058012450000001E-5</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>9.2095863490000002E-4</v>
       </c>
       <c r="H10" t="s">
@@ -1126,26 +1302,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>40</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>2015</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>123867</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>1.4446409960000001E-4</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>2.58229578E-3</v>
       </c>
       <c r="H11" t="s">
@@ -1155,26 +1331,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>40</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>2016</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="s">
         <v>29</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>123867</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>1.8006454949999999E-5</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>1.980710045E-4</v>
       </c>
       <c r="H12" t="s">
@@ -1184,26 +1360,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>40</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>2016</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="s">
         <v>29</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>149898</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>1.8006454949999999E-5</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>2.7009682430000001E-3</v>
       </c>
       <c r="H13" t="s">
@@ -1213,26 +1389,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>40</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>2017</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="s">
         <v>29</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>107157</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>1.8474583220000001E-5</v>
       </c>
-      <c r="G14">
+      <c r="G14" t="n">
         <v>1.4779666579999999E-4</v>
       </c>
       <c r="H14" t="s">
@@ -1242,26 +1418,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>40</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>2017</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="s">
         <v>29</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>123867</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>1.8474583220000001E-5</v>
       </c>
-      <c r="G15">
+      <c r="G15" t="n">
         <v>3.1406791479999998E-4</v>
       </c>
       <c r="H15" t="s">
@@ -1271,26 +1447,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>40</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>2017</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="s">
         <v>29</v>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>125131</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>5.5423749670000002E-5</v>
       </c>
-      <c r="G16">
+      <c r="G16" t="n">
         <v>1.8474583220000001E-5</v>
       </c>
       <c r="H16" t="s">
@@ -1300,26 +1476,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>40</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="n">
         <v>2017</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="s">
         <v>29</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>149898</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>1.8474583220000001E-5</v>
       </c>
-      <c r="G17">
+      <c r="G17" t="n">
         <v>2.1800008199999998E-3</v>
       </c>
       <c r="H17" t="s">
@@ -1329,26 +1505,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>40</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="n">
         <v>2018</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="s">
         <v>29</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>939</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>1.850168199E-5</v>
       </c>
-      <c r="G18">
+      <c r="G18" t="n">
         <v>3.7003363980000001E-5</v>
       </c>
       <c r="H18" t="s">
@@ -1358,26 +1534,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>40</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="n">
         <v>2018</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="s">
         <v>29</v>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>123803</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="n">
         <v>1.850168199E-5</v>
       </c>
-      <c r="G19">
+      <c r="G19" t="n">
         <v>8.3257568949999996E-4</v>
       </c>
       <c r="H19" t="s">
@@ -1387,26 +1563,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>40</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="n">
         <v>2018</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="s">
         <v>29</v>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>141101</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="n">
         <v>1.850168199E-5</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="n">
         <v>2.3201109210000001E-2</v>
       </c>
       <c r="H20" t="s">
@@ -1416,26 +1592,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>40</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="n">
         <v>2019</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="s">
         <v>29</v>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>107236</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>3.4976836589999999E-5</v>
       </c>
-      <c r="G21">
+      <c r="G21" t="n">
         <v>2.6232627440000002E-4</v>
       </c>
       <c r="H21" t="s">
@@ -1445,26 +1621,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>40</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="n">
         <v>2019</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="s">
         <v>29</v>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>123867</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>1.573957647E-4</v>
       </c>
-      <c r="G22">
+      <c r="G22" t="n">
         <v>1.9587028490000002E-3</v>
       </c>
       <c r="H22" t="s">
@@ -1474,26 +1650,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>40</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="n">
         <v>2019</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="s">
         <v>29</v>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>141101</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>1.7488418290000001E-5</v>
       </c>
-      <c r="G23">
+      <c r="G23" t="n">
         <v>1.1997054950000001E-2</v>
       </c>
       <c r="H23" t="s">
@@ -1503,26 +1679,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
         <v>40</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="n">
         <v>2020</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="s">
         <v>29</v>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>123867</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>1.8142426030000002E-5</v>
       </c>
-      <c r="G24">
+      <c r="G24" t="n">
         <v>3.6284852050000001E-4</v>
       </c>
       <c r="H24" t="s">
@@ -1532,26 +1708,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" t="s">
         <v>40</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="n">
         <v>2021</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="s">
         <v>29</v>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>107564</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>1.8528860369999999E-5</v>
       </c>
-      <c r="G25">
+      <c r="G25" t="n">
         <v>1.8528860369999999E-5</v>
       </c>
       <c r="H25" t="s">
@@ -1561,26 +1737,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" t="s">
         <v>40</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="n">
         <v>2021</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="s">
         <v>29</v>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>123867</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>1.8528860369999999E-5</v>
       </c>
-      <c r="G26">
+      <c r="G26" t="n">
         <v>5.55865811E-5</v>
       </c>
       <c r="H26" t="s">
@@ -1590,26 +1766,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" t="s">
         <v>40</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="n">
         <v>2022</v>
       </c>
-      <c r="C27">
+      <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="s">
         <v>29</v>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>123851</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="n">
         <v>1.697076582E-5</v>
       </c>
-      <c r="G27">
+      <c r="G27" t="n">
         <v>1.018245949E-4</v>
       </c>
       <c r="H27" t="s">
@@ -1619,26 +1795,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28" t="s">
         <v>40</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="n">
         <v>2022</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="s">
         <v>29</v>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>123908</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="n">
         <v>3.3941531640000001E-5</v>
       </c>
-      <c r="G28">
+      <c r="G28" t="n">
         <v>1.2218951390000001E-3</v>
       </c>
       <c r="H28" t="s">
@@ -1648,26 +1824,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" t="s">
         <v>40</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="n">
         <v>2022</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="s">
         <v>29</v>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>124048</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="n">
         <v>1.86678424E-4</v>
       </c>
-      <c r="G29">
+      <c r="G29" t="n">
         <v>5.6682357840000001E-3</v>
       </c>
       <c r="H29" t="s">
@@ -1684,665 +1860,786 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:S11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="19" max="19" width="11.42578125" style="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="E1" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="F1" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="G1" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="H1" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="I1" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="J1" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="K1" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="L1" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="M1" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="N1" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="O1" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="P1" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="Q1" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="R1" t="s">
-        <v>64</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="S1" t="s">
+        <v>108</v>
+      </c>
+      <c r="T1" t="s">
+        <v>109</v>
+      </c>
+      <c r="U1" t="s">
+        <v>110</v>
+      </c>
+      <c r="V1" t="s">
+        <v>111</v>
+      </c>
+      <c r="W1" t="s">
+        <v>112</v>
+      </c>
+      <c r="X1" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2">
+        <v>119</v>
+      </c>
+      <c r="D2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" t="n">
         <v>-3.754666667</v>
       </c>
-      <c r="E2">
-        <v>43.514583330000001</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>42.80146027</v>
+      <c r="F2" t="n">
+        <v>43.51458333</v>
+      </c>
+      <c r="G2" t="s">
+        <v>121</v>
       </c>
       <c r="H2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2">
+        <v>122</v>
+      </c>
+      <c r="I2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J2"/>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>124</v>
+      </c>
+      <c r="M2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N2"/>
+      <c r="O2" t="n">
+        <v>0.21125794553046</v>
+      </c>
+      <c r="P2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2" t="n">
+        <v>0.126630851885842</v>
+      </c>
+      <c r="T2" t="n">
         <v>57299.62</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L2" t="s">
-        <v>71</v>
-      </c>
-      <c r="M2">
-        <v>6.4398332833200001E-3</v>
-      </c>
-      <c r="N2">
-        <v>2.347310505894E-2</v>
-      </c>
-      <c r="O2">
-        <v>0.21125794553046001</v>
-      </c>
-      <c r="P2">
-        <v>6</v>
-      </c>
-      <c r="Q2">
-        <v>1.0231237200000001</v>
-      </c>
-      <c r="R2">
-        <v>1.5746223100000001</v>
-      </c>
-      <c r="S2" s="1">
-        <v>0.126630851885842</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U2" t="n">
+        <v>0.00643983328332</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.02347310505894</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.02312372</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.57462231</v>
+      </c>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>127</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3">
+        <v>119</v>
+      </c>
+      <c r="D3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" t="n">
         <v>-3.74675</v>
       </c>
-      <c r="E3">
-        <v>43.513500000000001</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>44.280708310000001</v>
+      <c r="F3" t="n">
+        <v>43.5135</v>
+      </c>
+      <c r="G3" t="s">
+        <v>121</v>
       </c>
       <c r="H3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3">
+        <v>129</v>
+      </c>
+      <c r="I3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M3" t="s">
+        <v>125</v>
+      </c>
+      <c r="N3"/>
+      <c r="O3" t="n">
+        <v>0.00333624972703</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3"/>
+      <c r="R3"/>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>56050.96</v>
       </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3" t="s">
-        <v>70</v>
-      </c>
-      <c r="L3" t="s">
-        <v>71</v>
-      </c>
-      <c r="M3">
-        <v>3.9249996785999997E-4</v>
-      </c>
-      <c r="N3">
-        <v>3.0329542972999999E-4</v>
-      </c>
-      <c r="O3">
-        <v>3.3362497270299999E-3</v>
-      </c>
-      <c r="P3">
+      <c r="U3" t="n">
+        <v>0.00039249996786</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.00030329542973</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.39074446</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.83303948</v>
+      </c>
+      <c r="Y3"/>
+      <c r="Z3"/>
+      <c r="AA3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-3.756666667</v>
+      </c>
+      <c r="F4" t="n">
+        <v>43.51475</v>
+      </c>
+      <c r="G4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H4" t="s">
+        <v>122</v>
+      </c>
+      <c r="I4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>124</v>
+      </c>
+      <c r="M4" t="s">
+        <v>125</v>
+      </c>
+      <c r="N4"/>
+      <c r="O4" t="n">
+        <v>0.035032544149</v>
+      </c>
+      <c r="P4" t="n">
         <v>2</v>
       </c>
-      <c r="Q3">
-        <v>-0.39074446000000002</v>
-      </c>
-      <c r="R3">
-        <v>-0.83303948000000005</v>
-      </c>
-      <c r="S3" s="1">
+      <c r="Q4"/>
+      <c r="R4"/>
+      <c r="S4" t="n">
+        <v>0.262886597953888</v>
+      </c>
+      <c r="T4" t="n">
+        <v>55377.08</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.0016252211205</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.0035032544149</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.82915385</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.79274315</v>
+      </c>
+      <c r="Y4"/>
+      <c r="Z4"/>
+      <c r="AA4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-3.75225</v>
+      </c>
+      <c r="F5" t="n">
+        <v>43.515</v>
+      </c>
+      <c r="G5" t="s">
+        <v>121</v>
+      </c>
+      <c r="H5" t="s">
+        <v>122</v>
+      </c>
+      <c r="I5" t="s">
+        <v>123</v>
+      </c>
+      <c r="J5"/>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>124</v>
+      </c>
+      <c r="M5" t="s">
+        <v>125</v>
+      </c>
+      <c r="N5"/>
+      <c r="O5" t="n">
+        <v>0.0202932747325</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5"/>
+      <c r="R5"/>
+      <c r="S5" t="n">
+        <v>0.931677018629255</v>
+      </c>
+      <c r="T5" t="n">
+        <v>55535.64</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.0002520903693</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.0028990392475</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.39427825</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.93374228</v>
+      </c>
+      <c r="Y5"/>
+      <c r="Z5"/>
+      <c r="AA5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-3.743166667</v>
+      </c>
+      <c r="F6" t="n">
+        <v>43.51408333</v>
+      </c>
+      <c r="G6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I6" t="s">
+        <v>123</v>
+      </c>
+      <c r="J6"/>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>124</v>
+      </c>
+      <c r="M6" t="s">
+        <v>125</v>
+      </c>
+      <c r="N6"/>
+      <c r="O6" t="n">
+        <v>0.04256543974112</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q6"/>
+      <c r="R6"/>
+      <c r="S6" t="n">
+        <v>0.819444444416357</v>
+      </c>
+      <c r="T6" t="n">
+        <v>54128.42</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.00177355998928</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.00266033998382</v>
+      </c>
+      <c r="W6" t="n">
+        <v>11.7300408</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.04722381</v>
+      </c>
+      <c r="Y6"/>
+      <c r="Z6"/>
+      <c r="AA6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" t="s">
+        <v>141</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-3.749333333</v>
+      </c>
+      <c r="F7" t="n">
+        <v>43.51325</v>
+      </c>
+      <c r="G7" t="s">
+        <v>121</v>
+      </c>
+      <c r="H7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I7" t="s">
+        <v>123</v>
+      </c>
+      <c r="J7"/>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>124</v>
+      </c>
+      <c r="M7" t="s">
+        <v>125</v>
+      </c>
+      <c r="N7"/>
+      <c r="O7" t="n">
+        <v>0.31291894742524</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7"/>
+      <c r="R7"/>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>54049.14</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.00072156559761</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.02407068826348</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-1.36801787</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.6248712</v>
+      </c>
+      <c r="Y7"/>
+      <c r="Z7"/>
+      <c r="AA7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D8" t="s">
+        <v>144</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-3.73825</v>
+      </c>
+      <c r="F8" t="n">
+        <v>43.513</v>
+      </c>
+      <c r="G8" t="s">
+        <v>121</v>
+      </c>
+      <c r="H8" t="s">
+        <v>145</v>
+      </c>
+      <c r="I8" t="s">
+        <v>123</v>
+      </c>
+      <c r="J8"/>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
+        <v>124</v>
+      </c>
+      <c r="M8" t="s">
+        <v>125</v>
+      </c>
+      <c r="N8"/>
+      <c r="O8" t="n">
+        <v>0.1137446725872</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8"/>
+      <c r="R8"/>
+      <c r="S8" t="n">
+        <v>0.843788437884171</v>
+      </c>
+      <c r="T8" t="n">
+        <v>57180.7</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.00167888815664</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.0142180840734</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08643439</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.74880432</v>
+      </c>
+      <c r="Y8"/>
+      <c r="Z8"/>
+      <c r="AA8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-3.74275</v>
+      </c>
+      <c r="F9" t="n">
+        <v>43.51341667</v>
+      </c>
+      <c r="G9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H9" t="s">
+        <v>129</v>
+      </c>
+      <c r="I9" t="s">
+        <v>123</v>
+      </c>
+      <c r="J9"/>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>124</v>
+      </c>
+      <c r="M9" t="s">
+        <v>125</v>
+      </c>
+      <c r="N9"/>
+      <c r="O9" t="n">
+        <v>0.002902788164</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9"/>
+      <c r="R9"/>
+      <c r="S9" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4">
-        <v>-3.7566666670000002</v>
-      </c>
-      <c r="E4">
-        <v>43.514749999999999</v>
-      </c>
-      <c r="F4">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>42.80146027</v>
-      </c>
-      <c r="H4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4">
-        <v>55377.08</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L4" t="s">
-        <v>71</v>
-      </c>
-      <c r="M4">
-        <v>1.6252211205E-3</v>
-      </c>
-      <c r="N4">
-        <v>3.5032544149000001E-3</v>
-      </c>
-      <c r="O4">
-        <v>3.5032544148999999E-2</v>
-      </c>
-      <c r="P4">
+      <c r="T9" t="n">
+        <v>55119.42</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.00014513940824</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.0003628485205</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9"/>
+      <c r="Z9"/>
+      <c r="AA9"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10" t="s">
+        <v>151</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-3.73625</v>
+      </c>
+      <c r="F10" t="n">
+        <v>43.51366667</v>
+      </c>
+      <c r="G10" t="s">
+        <v>121</v>
+      </c>
+      <c r="H10" t="s">
+        <v>145</v>
+      </c>
+      <c r="I10" t="s">
+        <v>123</v>
+      </c>
+      <c r="J10"/>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
+        <v>124</v>
+      </c>
+      <c r="M10" t="s">
+        <v>125</v>
+      </c>
+      <c r="N10"/>
+      <c r="O10" t="n">
+        <v>0.00044469264882</v>
+      </c>
+      <c r="P10" t="n">
         <v>2</v>
       </c>
-      <c r="Q4">
-        <v>0.82915384999999997</v>
-      </c>
-      <c r="R4">
-        <v>0.79274314999999995</v>
-      </c>
-      <c r="S4" s="1">
-        <v>0.26288659795388802</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5">
-        <v>-3.7522500000000001</v>
-      </c>
-      <c r="E5">
-        <v>43.515000000000001</v>
-      </c>
-      <c r="F5">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>42.80146027</v>
-      </c>
-      <c r="H5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5">
-        <v>55535.64</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
-        <v>70</v>
-      </c>
-      <c r="L5" t="s">
-        <v>71</v>
-      </c>
-      <c r="M5">
-        <v>2.5209036929999998E-4</v>
-      </c>
-      <c r="N5">
-        <v>2.8990392475000001E-3</v>
-      </c>
-      <c r="O5">
-        <v>2.0293274732500002E-2</v>
-      </c>
-      <c r="P5">
-        <v>2</v>
-      </c>
-      <c r="Q5">
-        <v>-0.39427825</v>
-      </c>
-      <c r="R5">
-        <v>0.93374228000000004</v>
-      </c>
-      <c r="S5" s="1">
-        <v>0.931677018629255</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6">
-        <v>-3.7431666670000001</v>
-      </c>
-      <c r="E6">
-        <v>43.514083329999998</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>44.280708310000001</v>
-      </c>
-      <c r="H6" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6">
-        <v>54128.42</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L6" t="s">
-        <v>71</v>
-      </c>
-      <c r="M6">
-        <v>1.77355998928E-3</v>
-      </c>
-      <c r="N6">
-        <v>2.6603399838200001E-3</v>
-      </c>
-      <c r="O6">
-        <v>4.2565439741120002E-2</v>
-      </c>
-      <c r="P6">
-        <v>4</v>
-      </c>
-      <c r="Q6">
-        <v>11.730040799999999</v>
-      </c>
-      <c r="R6">
-        <v>3.0472238100000002</v>
-      </c>
-      <c r="S6" s="1">
-        <v>0.819444444416357</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D7">
-        <v>-3.749333333</v>
-      </c>
-      <c r="E7">
-        <v>43.513249999999999</v>
-      </c>
-      <c r="F7">
-        <v>9</v>
-      </c>
-      <c r="G7">
-        <v>44.280708310000001</v>
-      </c>
-      <c r="H7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I7">
-        <v>54049.14</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
-        <v>70</v>
-      </c>
-      <c r="L7" t="s">
-        <v>71</v>
-      </c>
-      <c r="M7">
-        <v>7.2156559760999997E-4</v>
-      </c>
-      <c r="N7">
-        <v>2.4070688263480002E-2</v>
-      </c>
-      <c r="O7">
-        <v>0.31291894742524001</v>
-      </c>
-      <c r="P7">
+      <c r="Q10"/>
+      <c r="R10"/>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>53969.86</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.00022234632444</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.00007411544147</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.4056373</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.38193922</v>
+      </c>
+      <c r="Y10"/>
+      <c r="Z10"/>
+      <c r="AA10"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11" t="s">
+        <v>154</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-3.754666667</v>
+      </c>
+      <c r="F11" t="n">
+        <v>43.5145</v>
+      </c>
+      <c r="G11" t="s">
+        <v>121</v>
+      </c>
+      <c r="H11" t="s">
+        <v>122</v>
+      </c>
+      <c r="I11" t="s">
+        <v>123</v>
+      </c>
+      <c r="J11"/>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="s">
+        <v>124</v>
+      </c>
+      <c r="M11" t="s">
+        <v>125</v>
+      </c>
+      <c r="N11"/>
+      <c r="O11" t="n">
+        <v>0.0419517331074</v>
+      </c>
+      <c r="P11" t="n">
         <v>3</v>
       </c>
-      <c r="Q7">
-        <v>-1.3680178700000001</v>
-      </c>
-      <c r="R7">
-        <v>0.62487119999999996</v>
-      </c>
-      <c r="S7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8">
-        <v>-3.7382499999999999</v>
-      </c>
-      <c r="E8">
-        <v>43.512999999999998</v>
-      </c>
-      <c r="F8">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>45.999366760000001</v>
-      </c>
-      <c r="H8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8">
-        <v>57180.7</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8" t="s">
-        <v>70</v>
-      </c>
-      <c r="L8" t="s">
-        <v>71</v>
-      </c>
-      <c r="M8">
-        <v>1.6788881566399999E-3</v>
-      </c>
-      <c r="N8">
-        <v>1.42180840734E-2</v>
-      </c>
-      <c r="O8">
-        <v>0.1137446725872</v>
-      </c>
-      <c r="P8">
-        <v>3</v>
-      </c>
-      <c r="Q8">
-        <v>1.08643439</v>
-      </c>
-      <c r="R8">
-        <v>0.74880431999999997</v>
-      </c>
-      <c r="S8" s="1">
-        <v>0.84378843788417102</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9">
-        <v>-3.74275</v>
-      </c>
-      <c r="E9">
-        <v>43.513416669999998</v>
-      </c>
-      <c r="F9">
-        <v>9</v>
-      </c>
-      <c r="G9">
-        <v>44.280708310000001</v>
-      </c>
-      <c r="H9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9">
-        <v>55119.42</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>70</v>
-      </c>
-      <c r="L9" t="s">
-        <v>71</v>
-      </c>
-      <c r="M9">
-        <v>1.4513940824000001E-4</v>
-      </c>
-      <c r="N9">
-        <v>3.6284852050000001E-4</v>
-      </c>
-      <c r="O9">
-        <v>2.9027881640000001E-3</v>
-      </c>
-      <c r="P9">
-        <v>1</v>
-      </c>
-      <c r="Q9">
+      <c r="Q11"/>
+      <c r="R11"/>
+      <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10">
-        <v>-3.7362500000000001</v>
-      </c>
-      <c r="E10">
-        <v>43.513666669999999</v>
-      </c>
-      <c r="F10">
-        <v>9</v>
-      </c>
-      <c r="G10">
-        <v>45.999366760000001</v>
-      </c>
-      <c r="H10" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10">
-        <v>53969.86</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10" t="s">
-        <v>70</v>
-      </c>
-      <c r="L10" t="s">
-        <v>71</v>
-      </c>
-      <c r="M10">
-        <v>2.2234632443999999E-4</v>
-      </c>
-      <c r="N10">
-        <v>7.4115441470000006E-5</v>
-      </c>
-      <c r="O10">
-        <v>4.4469264882000001E-4</v>
-      </c>
-      <c r="P10">
-        <v>2</v>
-      </c>
-      <c r="Q10">
-        <v>-0.40563729999999998</v>
-      </c>
-      <c r="R10">
-        <v>-0.38193922000000002</v>
-      </c>
-      <c r="S10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11">
-        <v>-3.754666667</v>
-      </c>
-      <c r="E11">
-        <v>43.514499999999998</v>
-      </c>
-      <c r="F11">
-        <v>9</v>
-      </c>
-      <c r="G11">
-        <v>42.80146027</v>
-      </c>
-      <c r="H11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I11">
+      <c r="T11" t="n">
         <v>58924.86</v>
       </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L11" t="s">
-        <v>71</v>
-      </c>
-      <c r="M11">
-        <v>1.4255443287600001E-3</v>
-      </c>
-      <c r="N11">
-        <v>6.9919555179E-3</v>
-      </c>
-      <c r="O11">
-        <v>4.1951733107399997E-2</v>
-      </c>
-      <c r="P11">
-        <v>3</v>
-      </c>
-      <c r="Q11">
-        <v>0.93062884999999995</v>
-      </c>
-      <c r="R11">
-        <v>1.0220859099999999</v>
-      </c>
-      <c r="S11" s="1">
-        <v>0</v>
-      </c>
+      <c r="U11" t="n">
+        <v>0.00142554432876</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.0069919555179</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.93062885</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02208591</v>
+      </c>
+      <c r="Y11"/>
+      <c r="Z11"/>
+      <c r="AA11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2476,13 +2773,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9DCCBDA-7B19-4DE4-99D7-9199D220C4A7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5ABACD5-C438-4091-A339-E381C49DB2AB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{633D0B0D-0C21-414A-B7D2-9C4319F21706}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAC2881F-9721-42EC-8662-CFD96D122F08}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11A5F7F7-15A4-43B1-9EBD-D68F1EBE25E2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9E1A58F-8F74-4CF3-BA84-B1E731EDC065}"/>
 </file>